--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1308-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1308-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3A3E66-8E2F-4E55-B5FA-1B7E3B8D8C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B631ED64-B54D-4AFE-B435-2CB99F9910FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0F9D13E9-5018-4990-9682-AA26462002F6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{454F1CB9-169F-4324-AF11-6E3B7540D37D}"/>
   </bookViews>
   <sheets>
     <sheet name="1308-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1601,26 +1601,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00B76C7-08D8-489B-820B-EE6BE6109DE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C7E9BD-BEF5-43AE-87E4-406F00E4B998}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1654,7 +1653,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1690,7 +1689,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1742,7 +1741,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1810,7 +1809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1954,7 +1953,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2458,7 +2457,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2602,7 +2601,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2818,7 +2817,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2890,7 +2889,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2962,7 +2961,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3034,7 +3033,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3106,7 +3105,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3178,7 +3177,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3322,7 +3321,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3394,7 +3393,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3466,7 +3465,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3538,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3610,7 +3609,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3682,7 +3681,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>1998</v>
       </c>
@@ -3754,7 +3753,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
       <c r="C32" s="19" t="s">
@@ -3782,7 +3781,7 @@
       <c r="W32" s="51"/>
       <c r="X32" s="47"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="52">
         <v>1997</v>
       </c>
@@ -3854,7 +3853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
       <c r="B34" s="55"/>
       <c r="C34" s="21" t="s">
@@ -3882,7 +3881,7 @@
       <c r="W34" s="61"/>
       <c r="X34" s="57"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="42">
         <v>1996</v>
       </c>
@@ -3954,7 +3953,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="44"/>
       <c r="B36" s="45"/>
       <c r="C36" s="19" t="s">
@@ -3982,7 +3981,7 @@
       <c r="W36" s="51"/>
       <c r="X36" s="47"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>1995</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1994</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>1993</v>
       </c>
@@ -4198,7 +4197,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>1992</v>
       </c>
@@ -4270,7 +4269,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>1991</v>
       </c>
@@ -4342,7 +4341,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>1990</v>
       </c>
@@ -4414,7 +4413,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="52">
         <v>1989</v>
       </c>
@@ -4486,7 +4485,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="54"/>
       <c r="B44" s="55"/>
       <c r="C44" s="21" t="s">
@@ -4514,7 +4513,7 @@
       <c r="W44" s="61"/>
       <c r="X44" s="57"/>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1988</v>
       </c>
@@ -4586,7 +4585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1987</v>
       </c>
@@ -4658,7 +4657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1986</v>
       </c>
@@ -4730,7 +4729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1985</v>
       </c>
@@ -4802,7 +4801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1984</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>1983</v>
       </c>
@@ -4946,7 +4945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38" t="s">
         <v>68</v>
       </c>
